--- a/src/main/resources/baseFiles/excel/Reports.xlsx
+++ b/src/main/resources/baseFiles/excel/Reports.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3570" uniqueCount="887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4830" uniqueCount="1000">
   <si>
     <t>Firm</t>
   </si>
@@ -2689,6 +2689,345 @@
   </si>
   <si>
     <t>Rădulescu &amp; Mușoi</t>
+  </si>
+  <si>
+    <t>ALMT Legal</t>
+  </si>
+  <si>
+    <t>GKC Partners</t>
+  </si>
+  <si>
+    <t>Boase Cohen &amp; Collins</t>
+  </si>
+  <si>
+    <t>Anand &amp; Anand</t>
+  </si>
+  <si>
+    <t>Nagashima Ohno &amp; Tsunematsu</t>
+  </si>
+  <si>
+    <t>01min 40s</t>
+  </si>
+  <si>
+    <t>JIPYONG</t>
+  </si>
+  <si>
+    <t>Nuno Simões &amp; Associados</t>
+  </si>
+  <si>
+    <t>JunZeJun Law</t>
+  </si>
+  <si>
+    <t>Premier Chambers</t>
+  </si>
+  <si>
+    <t>Maheshwari &amp; Co</t>
+  </si>
+  <si>
+    <t>GLA &amp; Company</t>
+  </si>
+  <si>
+    <t>Saraf &amp; Partners</t>
+  </si>
+  <si>
+    <t>Machas &amp; Partners</t>
+  </si>
+  <si>
+    <t>PK WongAndNair</t>
+  </si>
+  <si>
+    <t>RSM</t>
+  </si>
+  <si>
+    <t>Mochtar Karuwin Komar</t>
+  </si>
+  <si>
+    <t>02min 21s</t>
+  </si>
+  <si>
+    <t>TAN Law</t>
+  </si>
+  <si>
+    <t>Longan Law</t>
+  </si>
+  <si>
+    <t>LAW Partnership</t>
+  </si>
+  <si>
+    <t>King Stubb &amp; Kasiva</t>
+  </si>
+  <si>
+    <t>Providence Law</t>
+  </si>
+  <si>
+    <t>MDP And Partners</t>
+  </si>
+  <si>
+    <t>Meysan</t>
+  </si>
+  <si>
+    <t>LHAG</t>
+  </si>
+  <si>
+    <t>Rajani Associates</t>
+  </si>
+  <si>
+    <t>MAQ Legal</t>
+  </si>
+  <si>
+    <t>Kim Chang &amp; Lee</t>
+  </si>
+  <si>
+    <t>Greenwood Roche</t>
+  </si>
+  <si>
+    <t>wilson ryan grose</t>
+  </si>
+  <si>
+    <t>Mayne Wetherell</t>
+  </si>
+  <si>
+    <t>LYND</t>
+  </si>
+  <si>
+    <t>Simont Braun</t>
+  </si>
+  <si>
+    <t>Mihaj, Ilić &amp; Milanović</t>
+  </si>
+  <si>
+    <t>LL Berg</t>
+  </si>
+  <si>
+    <t>Flichy Grangé</t>
+  </si>
+  <si>
+    <t>Pini Franco LLP</t>
+  </si>
+  <si>
+    <t>01min 56s</t>
+  </si>
+  <si>
+    <t>Fort Legal</t>
+  </si>
+  <si>
+    <t>Mermoz Avocats</t>
+  </si>
+  <si>
+    <t>MENA City Lawyers</t>
+  </si>
+  <si>
+    <t>Gütt Olk Feldhaus</t>
+  </si>
+  <si>
+    <t>Oppenhoff</t>
+  </si>
+  <si>
+    <t>LMS</t>
+  </si>
+  <si>
+    <t>Interlaw</t>
+  </si>
+  <si>
+    <t>Potamitis Vekris</t>
+  </si>
+  <si>
+    <t>GLX LTM</t>
+  </si>
+  <si>
+    <t>Pestalozzi</t>
+  </si>
+  <si>
+    <t>Kambourov &amp; Partners</t>
+  </si>
+  <si>
+    <t>RONN Law</t>
+  </si>
+  <si>
+    <t>Aman &amp; Partners</t>
+  </si>
+  <si>
+    <t>Wierzbowski &amp; Partners</t>
+  </si>
+  <si>
+    <t>Naschitz Brandes Amir</t>
+  </si>
+  <si>
+    <t>Maples</t>
+  </si>
+  <si>
+    <t>JLDAndMB Legal</t>
+  </si>
+  <si>
+    <t>McDermott Will &amp; Emery</t>
+  </si>
+  <si>
+    <t>Prager Dreifuss</t>
+  </si>
+  <si>
+    <t>Kvale</t>
+  </si>
+  <si>
+    <t>FTPA</t>
+  </si>
+  <si>
+    <t>Maikowski &amp; Ninnemann</t>
+  </si>
+  <si>
+    <t>RDS Partners</t>
+  </si>
+  <si>
+    <t>Greene &amp; Greene Solicitors</t>
+  </si>
+  <si>
+    <t>01min 07s</t>
+  </si>
+  <si>
+    <t>Zepos &amp; Yannopoulos</t>
+  </si>
+  <si>
+    <t>Gitti &amp; Partners</t>
+  </si>
+  <si>
+    <t>Niedermüller</t>
+  </si>
+  <si>
+    <t>SchalastAndPartner</t>
+  </si>
+  <si>
+    <t>DALDEWOLF</t>
+  </si>
+  <si>
+    <t>GvW Graf von Westphalen</t>
+  </si>
+  <si>
+    <t>Lacourte Raquin Tatar</t>
+  </si>
+  <si>
+    <t>Georgiev Todorov &amp; Co</t>
+  </si>
+  <si>
+    <t>Ortus</t>
+  </si>
+  <si>
+    <t>Granrut</t>
+  </si>
+  <si>
+    <t>Glade Michel Wirtz</t>
+  </si>
+  <si>
+    <t>Orsingher</t>
+  </si>
+  <si>
+    <t>Schellenberg Wittmer</t>
+  </si>
+  <si>
+    <t>NGL Legal</t>
+  </si>
+  <si>
+    <t>Niederhuber &amp; Partner</t>
+  </si>
+  <si>
+    <t>Cravath, Swaine &amp; Moore</t>
+  </si>
+  <si>
+    <t>Lenz &amp; Staehelin</t>
+  </si>
+  <si>
+    <t>MMD Advokati</t>
+  </si>
+  <si>
+    <t>Leitner Law Rechtsanwälte</t>
+  </si>
+  <si>
+    <t>Papapolitis &amp; Papapolitis</t>
+  </si>
+  <si>
+    <t>Sokol, Novák, Trojan, Doleček</t>
+  </si>
+  <si>
+    <t>Patrikios Pavlou &amp; Associates</t>
+  </si>
+  <si>
+    <t>id est avocats</t>
+  </si>
+  <si>
+    <t>Kaimakliotis</t>
+  </si>
+  <si>
+    <t>02min 19s</t>
+  </si>
+  <si>
+    <t>Grimaldi Alliance</t>
+  </si>
+  <si>
+    <t>MPR Partners</t>
+  </si>
+  <si>
+    <t>POELLATH</t>
+  </si>
+  <si>
+    <t>Ilej &amp; Partners</t>
+  </si>
+  <si>
+    <t>Giliberti Triscornia e Associati</t>
+  </si>
+  <si>
+    <t>Perchstone &amp; Graeys</t>
+  </si>
+  <si>
+    <t>Gleiss Lutz</t>
+  </si>
+  <si>
+    <t>MFW Fiałek</t>
+  </si>
+  <si>
+    <t>Sérvulo &amp; Associados</t>
+  </si>
+  <si>
+    <t>PLMJ</t>
+  </si>
+  <si>
+    <t>Macedo Vitorino</t>
+  </si>
+  <si>
+    <t>03min 24s</t>
+  </si>
+  <si>
+    <t>Peli Partners</t>
+  </si>
+  <si>
+    <t>Salus Legal</t>
+  </si>
+  <si>
+    <t>Mishcon de Reya</t>
+  </si>
+  <si>
+    <t>Snellman</t>
+  </si>
+  <si>
+    <t>Provença de Carvalho</t>
+  </si>
+  <si>
+    <t>Riad Saleh &amp; Partners</t>
+  </si>
+  <si>
+    <t>HFW</t>
+  </si>
+  <si>
+    <t>LPA Law Firm</t>
+  </si>
+  <si>
+    <t>02min 50s</t>
+  </si>
+  <si>
+    <t>Gomez Acebo &amp; Pombo</t>
+  </si>
+  <si>
+    <t>JPM &amp; Partners</t>
+  </si>
+  <si>
+    <t>02min 52s</t>
   </si>
 </sst>
 </file>
@@ -3676,7 +4015,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C421"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" customWidth="true" style="1" width="27.6634615384615"/>
@@ -3692,6 +4031,4626 @@
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="1">
+        <v>887</v>
+      </c>
+      <c r="B2" t="s" s="1">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="1">
+        <v>249</v>
+      </c>
+      <c r="B3" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="1">
+        <v>224</v>
+      </c>
+      <c r="B4" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="1">
+        <v>257</v>
+      </c>
+      <c r="B5" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C5" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="1">
+        <v>888</v>
+      </c>
+      <c r="B6" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="1">
+        <v>246</v>
+      </c>
+      <c r="B7" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C7" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="1">
+        <v>798</v>
+      </c>
+      <c r="B8" t="s" s="1">
+        <v>425</v>
+      </c>
+      <c r="C8" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="1">
+        <v>104</v>
+      </c>
+      <c r="B9" t="s" s="1">
+        <v>520</v>
+      </c>
+      <c r="C9" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="1">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="1">
+        <v>146</v>
+      </c>
+      <c r="B11" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="1">
+        <v>889</v>
+      </c>
+      <c r="B12" t="s" s="1">
+        <v>157</v>
+      </c>
+      <c r="C12" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="1">
+        <v>203</v>
+      </c>
+      <c r="B13" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="1">
+        <v>846</v>
+      </c>
+      <c r="B14" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="1">
+        <v>890</v>
+      </c>
+      <c r="B15" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="C15" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="1">
+        <v>66</v>
+      </c>
+      <c r="B16" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="1">
+        <v>119</v>
+      </c>
+      <c r="B17" t="s" s="1">
+        <v>721</v>
+      </c>
+      <c r="C17" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="1">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s" s="1">
+        <v>215</v>
+      </c>
+      <c r="C18" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="1">
+        <v>164</v>
+      </c>
+      <c r="B19" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C19" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="1">
+        <v>102</v>
+      </c>
+      <c r="B20" t="s" s="1">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="1">
+        <v>891</v>
+      </c>
+      <c r="B21" t="s" s="1">
+        <v>739</v>
+      </c>
+      <c r="C21" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="1">
+        <v>166</v>
+      </c>
+      <c r="B22" t="s" s="1">
+        <v>892</v>
+      </c>
+      <c r="C22" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="1">
+        <v>181</v>
+      </c>
+      <c r="B23" t="s" s="1">
+        <v>134</v>
+      </c>
+      <c r="C23" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="1">
+        <v>893</v>
+      </c>
+      <c r="B24" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="C24" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="1">
+        <v>824</v>
+      </c>
+      <c r="B25" t="s" s="1">
+        <v>101</v>
+      </c>
+      <c r="C25" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="1">
+        <v>209</v>
+      </c>
+      <c r="B26" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="1">
+        <v>894</v>
+      </c>
+      <c r="B27" t="s" s="1">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="1">
+        <v>173</v>
+      </c>
+      <c r="B28" t="s" s="1">
+        <v>134</v>
+      </c>
+      <c r="C28" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="1">
+        <v>258</v>
+      </c>
+      <c r="B29" t="s" s="1">
+        <v>308</v>
+      </c>
+      <c r="C29" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="1">
+        <v>186</v>
+      </c>
+      <c r="B30" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C30" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="1">
+        <v>50</v>
+      </c>
+      <c r="B31" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="C31" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="1">
+        <v>895</v>
+      </c>
+      <c r="B32" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="C32" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="1">
+        <v>797</v>
+      </c>
+      <c r="B33" t="s" s="1">
+        <v>144</v>
+      </c>
+      <c r="C33" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s" s="1">
+        <v>585</v>
+      </c>
+      <c r="C34" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="1">
+        <v>896</v>
+      </c>
+      <c r="B35" t="s" s="1">
+        <v>86</v>
+      </c>
+      <c r="C35" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="1">
+        <v>117</v>
+      </c>
+      <c r="B36" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C36" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="1">
+        <v>897</v>
+      </c>
+      <c r="B37" t="s" s="1">
+        <v>549</v>
+      </c>
+      <c r="C37" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="1">
+        <v>188</v>
+      </c>
+      <c r="B38" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C38" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="B39" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="C39" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="1">
+        <v>127</v>
+      </c>
+      <c r="B40" t="s" s="1">
+        <v>116</v>
+      </c>
+      <c r="C40" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="1">
+        <v>898</v>
+      </c>
+      <c r="B41" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C41" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="1">
+        <v>813</v>
+      </c>
+      <c r="B42" t="s" s="1">
+        <v>101</v>
+      </c>
+      <c r="C42" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="1">
+        <v>899</v>
+      </c>
+      <c r="B43" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="1">
+        <v>837</v>
+      </c>
+      <c r="B44" t="s" s="1">
+        <v>174</v>
+      </c>
+      <c r="C44" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="1">
+        <v>223</v>
+      </c>
+      <c r="B45" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="C45" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="1">
+        <v>812</v>
+      </c>
+      <c r="B46" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C46" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B47" t="s" s="1">
+        <v>495</v>
+      </c>
+      <c r="C47" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B48" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C48" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="1">
+        <v>100</v>
+      </c>
+      <c r="B49" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="C49" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="1">
+        <v>168</v>
+      </c>
+      <c r="B50" t="s" s="1">
+        <v>130</v>
+      </c>
+      <c r="C50" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="1">
+        <v>140</v>
+      </c>
+      <c r="B51" t="s" s="1">
+        <v>49</v>
+      </c>
+      <c r="C51" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="1">
+        <v>900</v>
+      </c>
+      <c r="B52" t="s" s="1">
+        <v>101</v>
+      </c>
+      <c r="C52" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="1">
+        <v>854</v>
+      </c>
+      <c r="B53" t="s" s="1">
+        <v>128</v>
+      </c>
+      <c r="C53" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="1">
+        <v>901</v>
+      </c>
+      <c r="B54" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C54" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="1">
+        <v>902</v>
+      </c>
+      <c r="B55" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="C55" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="1">
+        <v>121</v>
+      </c>
+      <c r="B56" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C56" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="1">
+        <v>810</v>
+      </c>
+      <c r="B57" t="s" s="1">
+        <v>96</v>
+      </c>
+      <c r="C57" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="1">
+        <v>230</v>
+      </c>
+      <c r="B58" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C58" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="1">
+        <v>903</v>
+      </c>
+      <c r="B59" t="s" s="1">
+        <v>904</v>
+      </c>
+      <c r="C59" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="1">
+        <v>905</v>
+      </c>
+      <c r="B60" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="C60" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="1">
+        <v>219</v>
+      </c>
+      <c r="B61" t="s" s="1">
+        <v>116</v>
+      </c>
+      <c r="C61" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="1">
+        <v>906</v>
+      </c>
+      <c r="B62" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="C62" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="1">
+        <v>252</v>
+      </c>
+      <c r="B63" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="C63" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="1">
+        <v>907</v>
+      </c>
+      <c r="B64" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="C64" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="1">
+        <v>143</v>
+      </c>
+      <c r="B65" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="C65" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="1">
+        <v>908</v>
+      </c>
+      <c r="B66" t="s" s="1">
+        <v>134</v>
+      </c>
+      <c r="C66" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="1">
+        <v>909</v>
+      </c>
+      <c r="B67" t="s" s="1">
+        <v>49</v>
+      </c>
+      <c r="C67" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="1">
+        <v>910</v>
+      </c>
+      <c r="B68" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="C68" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="1">
+        <v>911</v>
+      </c>
+      <c r="B69" t="s" s="1">
+        <v>312</v>
+      </c>
+      <c r="C69" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="1">
+        <v>64</v>
+      </c>
+      <c r="B70" t="s" s="1">
+        <v>49</v>
+      </c>
+      <c r="C70" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="1">
+        <v>210</v>
+      </c>
+      <c r="B71" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="C71" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="1">
+        <v>852</v>
+      </c>
+      <c r="B72" t="s" s="1">
+        <v>176</v>
+      </c>
+      <c r="C72" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="1">
+        <v>912</v>
+      </c>
+      <c r="B73" t="s" s="1">
+        <v>176</v>
+      </c>
+      <c r="C73" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="1">
+        <v>192</v>
+      </c>
+      <c r="B74" t="s" s="1">
+        <v>193</v>
+      </c>
+      <c r="C74" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="1">
+        <v>913</v>
+      </c>
+      <c r="B75" t="s" s="1">
+        <v>280</v>
+      </c>
+      <c r="C75" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="1">
+        <v>199</v>
+      </c>
+      <c r="B76" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="C76" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="1">
+        <v>238</v>
+      </c>
+      <c r="B77" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="C77" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="1">
+        <v>227</v>
+      </c>
+      <c r="B78" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="C78" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="1">
+        <v>198</v>
+      </c>
+      <c r="B79" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="C79" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="1">
+        <v>914</v>
+      </c>
+      <c r="B80" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="C80" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="1">
+        <v>915</v>
+      </c>
+      <c r="B81" t="s" s="1">
+        <v>80</v>
+      </c>
+      <c r="C81" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="1">
+        <v>275</v>
+      </c>
+      <c r="B82" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="C82" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="1">
+        <v>916</v>
+      </c>
+      <c r="B83" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="C83" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="1">
+        <v>297</v>
+      </c>
+      <c r="B84" t="s" s="1">
+        <v>75</v>
+      </c>
+      <c r="C84" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="1">
+        <v>917</v>
+      </c>
+      <c r="B85" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="C85" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="1">
+        <v>293</v>
+      </c>
+      <c r="B86" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C86" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="1">
+        <v>309</v>
+      </c>
+      <c r="B87" t="s" s="1">
+        <v>130</v>
+      </c>
+      <c r="C87" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="1">
+        <v>314</v>
+      </c>
+      <c r="B88" t="s" s="1">
+        <v>82</v>
+      </c>
+      <c r="C88" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="1">
+        <v>278</v>
+      </c>
+      <c r="B89" t="s" s="1">
+        <v>461</v>
+      </c>
+      <c r="C89" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="1">
+        <v>871</v>
+      </c>
+      <c r="B90" t="s" s="1">
+        <v>500</v>
+      </c>
+      <c r="C90" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="1">
+        <v>862</v>
+      </c>
+      <c r="B91" t="s" s="1">
+        <v>80</v>
+      </c>
+      <c r="C91" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="1">
+        <v>267</v>
+      </c>
+      <c r="B92" t="s" s="1">
+        <v>82</v>
+      </c>
+      <c r="C92" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="1">
+        <v>918</v>
+      </c>
+      <c r="B93" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="C93" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="1">
+        <v>284</v>
+      </c>
+      <c r="B94" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="C94" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="1">
+        <v>870</v>
+      </c>
+      <c r="B95" t="s" s="1">
+        <v>155</v>
+      </c>
+      <c r="C95" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="1">
+        <v>279</v>
+      </c>
+      <c r="B96" t="s" s="1">
+        <v>443</v>
+      </c>
+      <c r="C96" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="1">
+        <v>373</v>
+      </c>
+      <c r="B97" t="s" s="1">
+        <v>443</v>
+      </c>
+      <c r="C97" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="1">
+        <v>919</v>
+      </c>
+      <c r="B98" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="C98" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="1">
+        <v>634</v>
+      </c>
+      <c r="B99" t="s" s="1">
+        <v>134</v>
+      </c>
+      <c r="C99" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="1">
+        <v>337</v>
+      </c>
+      <c r="B100" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="C100" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="1">
+        <v>478</v>
+      </c>
+      <c r="B101" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="C101" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="1">
+        <v>534</v>
+      </c>
+      <c r="B102" t="s" s="1">
+        <v>191</v>
+      </c>
+      <c r="C102" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="1">
+        <v>568</v>
+      </c>
+      <c r="B103" t="s" s="1">
+        <v>547</v>
+      </c>
+      <c r="C103" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="1">
+        <v>539</v>
+      </c>
+      <c r="B104" t="s" s="1">
+        <v>878</v>
+      </c>
+      <c r="C104" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="1">
+        <v>640</v>
+      </c>
+      <c r="B105" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="C105" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="1">
+        <v>920</v>
+      </c>
+      <c r="B106" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="C106" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="1">
+        <v>580</v>
+      </c>
+      <c r="B107" t="s" s="1">
+        <v>130</v>
+      </c>
+      <c r="C107" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="1">
+        <v>333</v>
+      </c>
+      <c r="B108" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C108" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="1">
+        <v>561</v>
+      </c>
+      <c r="B109" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C109" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="1">
+        <v>556</v>
+      </c>
+      <c r="B110" t="s" s="1">
+        <v>576</v>
+      </c>
+      <c r="C110" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="1">
+        <v>566</v>
+      </c>
+      <c r="B111" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C111" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="1">
+        <v>628</v>
+      </c>
+      <c r="B112" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C112" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="1">
+        <v>459</v>
+      </c>
+      <c r="B113" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="C113" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="1">
+        <v>372</v>
+      </c>
+      <c r="B114" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C114" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="1">
+        <v>466</v>
+      </c>
+      <c r="B115" t="s" s="1">
+        <v>107</v>
+      </c>
+      <c r="C115" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="1">
+        <v>538</v>
+      </c>
+      <c r="B116" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="C116" t="s" s="1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="1">
+        <v>512</v>
+      </c>
+      <c r="B117" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C117" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="1">
+        <v>921</v>
+      </c>
+      <c r="B118" t="s" s="1">
+        <v>125</v>
+      </c>
+      <c r="C118" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="1">
+        <v>922</v>
+      </c>
+      <c r="B119" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="C119" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="1">
+        <v>548</v>
+      </c>
+      <c r="B120" t="s" s="1">
+        <v>560</v>
+      </c>
+      <c r="C120" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="1">
+        <v>616</v>
+      </c>
+      <c r="B121" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="C121" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="1">
+        <v>617</v>
+      </c>
+      <c r="B122" t="s" s="1">
+        <v>648</v>
+      </c>
+      <c r="C122" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="1">
+        <v>536</v>
+      </c>
+      <c r="B123" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C123" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="1">
+        <v>498</v>
+      </c>
+      <c r="B124" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C124" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="1">
+        <v>639</v>
+      </c>
+      <c r="B125" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C125" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="1">
+        <v>545</v>
+      </c>
+      <c r="B126" t="s" s="1">
+        <v>80</v>
+      </c>
+      <c r="C126" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="1">
+        <v>565</v>
+      </c>
+      <c r="B127" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C127" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="1">
+        <v>923</v>
+      </c>
+      <c r="B128" t="s" s="1">
+        <v>328</v>
+      </c>
+      <c r="C128" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="1">
+        <v>629</v>
+      </c>
+      <c r="B129" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="C129" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="1">
+        <v>325</v>
+      </c>
+      <c r="B130" t="s" s="1">
+        <v>277</v>
+      </c>
+      <c r="C130" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="1">
+        <v>620</v>
+      </c>
+      <c r="B131" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="C131" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="1">
+        <v>924</v>
+      </c>
+      <c r="B132" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="C132" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="1">
+        <v>558</v>
+      </c>
+      <c r="B133" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C133" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="1">
+        <v>278</v>
+      </c>
+      <c r="B134" t="s" s="1">
+        <v>925</v>
+      </c>
+      <c r="C134" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="1">
+        <v>550</v>
+      </c>
+      <c r="B135" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="C135" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="1">
+        <v>926</v>
+      </c>
+      <c r="B136" t="s" s="1">
+        <v>101</v>
+      </c>
+      <c r="C136" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="1">
+        <v>618</v>
+      </c>
+      <c r="B137" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="C137" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="1">
+        <v>474</v>
+      </c>
+      <c r="B138" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C138" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="1">
+        <v>927</v>
+      </c>
+      <c r="B139" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="C139" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="1">
+        <v>319</v>
+      </c>
+      <c r="B140" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="C140" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="1">
+        <v>350</v>
+      </c>
+      <c r="B141" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="C141" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="1">
+        <v>589</v>
+      </c>
+      <c r="B142" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C142" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="1">
+        <v>541</v>
+      </c>
+      <c r="B143" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C143" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="1">
+        <v>516</v>
+      </c>
+      <c r="B144" t="s" s="1">
+        <v>75</v>
+      </c>
+      <c r="C144" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="1">
+        <v>928</v>
+      </c>
+      <c r="B145" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="C145" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="1">
+        <v>531</v>
+      </c>
+      <c r="B146" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="C146" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="1">
+        <v>929</v>
+      </c>
+      <c r="B147" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C147" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="1">
+        <v>597</v>
+      </c>
+      <c r="B148" t="s" s="1">
+        <v>884</v>
+      </c>
+      <c r="C148" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="1">
+        <v>483</v>
+      </c>
+      <c r="B149" t="s" s="1">
+        <v>487</v>
+      </c>
+      <c r="C149" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="1">
+        <v>595</v>
+      </c>
+      <c r="B150" t="s" s="1">
+        <v>82</v>
+      </c>
+      <c r="C150" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="1">
+        <v>387</v>
+      </c>
+      <c r="B151" t="s" s="1">
+        <v>86</v>
+      </c>
+      <c r="C151" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="1">
+        <v>524</v>
+      </c>
+      <c r="B152" t="s" s="1">
+        <v>176</v>
+      </c>
+      <c r="C152" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="1">
+        <v>411</v>
+      </c>
+      <c r="B153" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="C153" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="1">
+        <v>530</v>
+      </c>
+      <c r="B154" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="C154" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="1">
+        <v>596</v>
+      </c>
+      <c r="B155" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="C155" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="1">
+        <v>930</v>
+      </c>
+      <c r="B156" t="s" s="1">
+        <v>101</v>
+      </c>
+      <c r="C156" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="1">
+        <v>405</v>
+      </c>
+      <c r="B157" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="C157" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="1">
+        <v>448</v>
+      </c>
+      <c r="B158" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="C158" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="1">
+        <v>601</v>
+      </c>
+      <c r="B159" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="C159" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="1">
+        <v>351</v>
+      </c>
+      <c r="B160" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="C160" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="1">
+        <v>931</v>
+      </c>
+      <c r="B161" t="s" s="1">
+        <v>101</v>
+      </c>
+      <c r="C161" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="1">
+        <v>376</v>
+      </c>
+      <c r="B162" t="s" s="1">
+        <v>82</v>
+      </c>
+      <c r="C162" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="1">
+        <v>430</v>
+      </c>
+      <c r="B163" t="s" s="1">
+        <v>386</v>
+      </c>
+      <c r="C163" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="1">
+        <v>382</v>
+      </c>
+      <c r="B164" t="s" s="1">
+        <v>391</v>
+      </c>
+      <c r="C164" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="1">
+        <v>932</v>
+      </c>
+      <c r="B165" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C165" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="1">
+        <v>633</v>
+      </c>
+      <c r="B166" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="C166" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="1">
+        <v>933</v>
+      </c>
+      <c r="B167" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="C167" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="1">
+        <v>490</v>
+      </c>
+      <c r="B168" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C168" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="1">
+        <v>523</v>
+      </c>
+      <c r="B169" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C169" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="1">
+        <v>934</v>
+      </c>
+      <c r="B170" t="s" s="1">
+        <v>215</v>
+      </c>
+      <c r="C170" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="1">
+        <v>380</v>
+      </c>
+      <c r="B171" t="s" s="1">
+        <v>487</v>
+      </c>
+      <c r="C171" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="1">
+        <v>454</v>
+      </c>
+      <c r="B172" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C172" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="1">
+        <v>602</v>
+      </c>
+      <c r="B173" t="s" s="1">
+        <v>141</v>
+      </c>
+      <c r="C173" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="1">
+        <v>322</v>
+      </c>
+      <c r="B174" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="C174" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="1">
+        <v>935</v>
+      </c>
+      <c r="B175" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="C175" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="1">
+        <v>396</v>
+      </c>
+      <c r="B176" t="s" s="1">
+        <v>86</v>
+      </c>
+      <c r="C176" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="1">
+        <v>936</v>
+      </c>
+      <c r="B177" t="s" s="1">
+        <v>386</v>
+      </c>
+      <c r="C177" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="1">
+        <v>513</v>
+      </c>
+      <c r="B178" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C178" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="1">
+        <v>384</v>
+      </c>
+      <c r="B179" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C179" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="1">
+        <v>476</v>
+      </c>
+      <c r="B180" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C180" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="1">
+        <v>937</v>
+      </c>
+      <c r="B181" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C181" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="1">
+        <v>317</v>
+      </c>
+      <c r="B182" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C182" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="1">
+        <v>492</v>
+      </c>
+      <c r="B183" t="s" s="1">
+        <v>130</v>
+      </c>
+      <c r="C183" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="1">
+        <v>475</v>
+      </c>
+      <c r="B184" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C184" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="1">
+        <v>537</v>
+      </c>
+      <c r="B185" t="s" s="1">
+        <v>312</v>
+      </c>
+      <c r="C185" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="1">
+        <v>938</v>
+      </c>
+      <c r="B186" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C186" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="1">
+        <v>626</v>
+      </c>
+      <c r="B187" t="s" s="1">
+        <v>176</v>
+      </c>
+      <c r="C187" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="1">
+        <v>335</v>
+      </c>
+      <c r="B188" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C188" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="1">
+        <v>323</v>
+      </c>
+      <c r="B189" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="C189" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="1">
+        <v>442</v>
+      </c>
+      <c r="B190" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C190" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="1">
+        <v>939</v>
+      </c>
+      <c r="B191" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="C191" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="1">
+        <v>447</v>
+      </c>
+      <c r="B192" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="C192" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="1">
+        <v>940</v>
+      </c>
+      <c r="B193" t="s" s="1">
+        <v>144</v>
+      </c>
+      <c r="C193" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="1">
+        <v>482</v>
+      </c>
+      <c r="B194" t="s" s="1">
+        <v>500</v>
+      </c>
+      <c r="C194" t="s" s="1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="1">
+        <v>406</v>
+      </c>
+      <c r="B195" t="s" s="1">
+        <v>75</v>
+      </c>
+      <c r="C195" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="1">
+        <v>941</v>
+      </c>
+      <c r="B196" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="C196" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="1">
+        <v>343</v>
+      </c>
+      <c r="B197" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C197" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="1">
+        <v>942</v>
+      </c>
+      <c r="B198" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C198" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="1">
+        <v>437</v>
+      </c>
+      <c r="B199" t="s" s="1">
+        <v>487</v>
+      </c>
+      <c r="C199" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="1">
+        <v>943</v>
+      </c>
+      <c r="B200" t="s" s="1">
+        <v>280</v>
+      </c>
+      <c r="C200" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="1">
+        <v>359</v>
+      </c>
+      <c r="B201" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="C201" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="1">
+        <v>352</v>
+      </c>
+      <c r="B202" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="C202" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="1">
+        <v>354</v>
+      </c>
+      <c r="B203" t="s" s="1">
+        <v>817</v>
+      </c>
+      <c r="C203" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="1">
+        <v>625</v>
+      </c>
+      <c r="B204" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="C204" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="1">
+        <v>944</v>
+      </c>
+      <c r="B205" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="C205" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="1">
+        <v>410</v>
+      </c>
+      <c r="B206" t="s" s="1">
+        <v>451</v>
+      </c>
+      <c r="C206" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="1">
+        <v>378</v>
+      </c>
+      <c r="B207" t="s" s="1">
+        <v>141</v>
+      </c>
+      <c r="C207" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="1">
+        <v>473</v>
+      </c>
+      <c r="B208" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="C208" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="1">
+        <v>444</v>
+      </c>
+      <c r="B209" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C209" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="1">
+        <v>413</v>
+      </c>
+      <c r="B210" t="s" s="1">
+        <v>328</v>
+      </c>
+      <c r="C210" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="1">
+        <v>591</v>
+      </c>
+      <c r="B211" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="C211" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="1">
+        <v>945</v>
+      </c>
+      <c r="B212" t="s" s="1">
+        <v>220</v>
+      </c>
+      <c r="C212" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="1">
+        <v>559</v>
+      </c>
+      <c r="B213" t="s" s="1">
+        <v>312</v>
+      </c>
+      <c r="C213" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="1">
+        <v>946</v>
+      </c>
+      <c r="B214" t="s" s="1">
+        <v>7</v>
+      </c>
+      <c r="C214" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="1">
+        <v>613</v>
+      </c>
+      <c r="B215" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="C215" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="1">
+        <v>488</v>
+      </c>
+      <c r="B216" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="C216" t="s" s="1">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="1">
+        <v>947</v>
+      </c>
+      <c r="B217" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="C217" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="1">
+        <v>330</v>
+      </c>
+      <c r="B218" t="s" s="1">
+        <v>391</v>
+      </c>
+      <c r="C218" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="1">
+        <v>397</v>
+      </c>
+      <c r="B219" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="C219" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="1">
+        <v>510</v>
+      </c>
+      <c r="B220" t="s" s="1">
+        <v>650</v>
+      </c>
+      <c r="C220" t="s" s="1">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="1">
+        <v>948</v>
+      </c>
+      <c r="B221" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C221" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="1">
+        <v>949</v>
+      </c>
+      <c r="B222" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C222" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="1">
+        <v>632</v>
+      </c>
+      <c r="B223" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C223" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="1">
+        <v>453</v>
+      </c>
+      <c r="B224" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="C224" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="1">
+        <v>320</v>
+      </c>
+      <c r="B225" t="s" s="1">
+        <v>49</v>
+      </c>
+      <c r="C225" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="1">
+        <v>611</v>
+      </c>
+      <c r="B226" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C226" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="1">
+        <v>419</v>
+      </c>
+      <c r="B227" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="C227" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="1">
+        <v>433</v>
+      </c>
+      <c r="B228" t="s" s="1">
+        <v>950</v>
+      </c>
+      <c r="C228" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="1">
+        <v>366</v>
+      </c>
+      <c r="B229" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="C229" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="1">
+        <v>586</v>
+      </c>
+      <c r="B230" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="C230" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="1">
+        <v>469</v>
+      </c>
+      <c r="B231" t="s" s="1">
+        <v>116</v>
+      </c>
+      <c r="C231" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="1">
+        <v>951</v>
+      </c>
+      <c r="B232" t="s" s="1">
+        <v>144</v>
+      </c>
+      <c r="C232" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="1">
+        <v>952</v>
+      </c>
+      <c r="B233" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="C233" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="1">
+        <v>436</v>
+      </c>
+      <c r="B234" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="C234" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="1">
+        <v>953</v>
+      </c>
+      <c r="B235" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C235" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="1">
+        <v>458</v>
+      </c>
+      <c r="B236" t="s" s="1">
+        <v>7</v>
+      </c>
+      <c r="C236" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="1">
+        <v>610</v>
+      </c>
+      <c r="B237" t="s" s="1">
+        <v>328</v>
+      </c>
+      <c r="C237" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="1">
+        <v>552</v>
+      </c>
+      <c r="B238" t="s" s="1">
+        <v>82</v>
+      </c>
+      <c r="C238" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="1">
+        <v>452</v>
+      </c>
+      <c r="B239" t="s" s="1">
+        <v>215</v>
+      </c>
+      <c r="C239" t="s" s="1">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="1">
+        <v>363</v>
+      </c>
+      <c r="B240" t="s" s="1">
+        <v>811</v>
+      </c>
+      <c r="C240" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="1">
+        <v>954</v>
+      </c>
+      <c r="B241" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C241" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="1">
+        <v>955</v>
+      </c>
+      <c r="B242" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C242" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="1">
+        <v>509</v>
+      </c>
+      <c r="B243" t="s" s="1">
+        <v>82</v>
+      </c>
+      <c r="C243" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="1">
+        <v>668</v>
+      </c>
+      <c r="B244" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="C244" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="1">
+        <v>956</v>
+      </c>
+      <c r="B245" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="C245" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="1">
+        <v>471</v>
+      </c>
+      <c r="B246" t="s" s="1">
+        <v>547</v>
+      </c>
+      <c r="C246" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="1">
+        <v>957</v>
+      </c>
+      <c r="B247" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C247" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="1">
+        <v>958</v>
+      </c>
+      <c r="B248" t="s" s="1">
+        <v>75</v>
+      </c>
+      <c r="C248" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="1">
+        <v>581</v>
+      </c>
+      <c r="B249" t="s" s="1">
+        <v>101</v>
+      </c>
+      <c r="C249" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="1">
+        <v>376</v>
+      </c>
+      <c r="B250" t="s" s="1">
+        <v>174</v>
+      </c>
+      <c r="C250" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="1">
+        <v>959</v>
+      </c>
+      <c r="B251" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C251" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="1">
+        <v>381</v>
+      </c>
+      <c r="B252" t="s" s="1">
+        <v>141</v>
+      </c>
+      <c r="C252" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="1">
+        <v>491</v>
+      </c>
+      <c r="B253" t="s" s="1">
+        <v>86</v>
+      </c>
+      <c r="C253" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="1">
+        <v>374</v>
+      </c>
+      <c r="B254" t="s" s="1">
+        <v>721</v>
+      </c>
+      <c r="C254" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="1">
+        <v>573</v>
+      </c>
+      <c r="B255" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C255" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="1">
+        <v>960</v>
+      </c>
+      <c r="B256" t="s" s="1">
+        <v>82</v>
+      </c>
+      <c r="C256" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="1">
+        <v>508</v>
+      </c>
+      <c r="B257" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="C257" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="1">
+        <v>400</v>
+      </c>
+      <c r="B258" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C258" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="1">
+        <v>572</v>
+      </c>
+      <c r="B259" t="s" s="1">
+        <v>176</v>
+      </c>
+      <c r="C259" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="1">
+        <v>401</v>
+      </c>
+      <c r="B260" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C260" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="1">
+        <v>627</v>
+      </c>
+      <c r="B261" t="s" s="1">
+        <v>7</v>
+      </c>
+      <c r="C261" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="1">
+        <v>612</v>
+      </c>
+      <c r="B262" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="C262" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="1">
+        <v>346</v>
+      </c>
+      <c r="B263" t="s" s="1">
+        <v>521</v>
+      </c>
+      <c r="C263" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="1">
+        <v>420</v>
+      </c>
+      <c r="B264" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="C264" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="1">
+        <v>961</v>
+      </c>
+      <c r="B265" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="C265" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="1">
+        <v>389</v>
+      </c>
+      <c r="B266" t="s" s="1">
+        <v>144</v>
+      </c>
+      <c r="C266" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="1">
+        <v>962</v>
+      </c>
+      <c r="B267" t="s" s="1">
+        <v>101</v>
+      </c>
+      <c r="C267" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="1">
+        <v>963</v>
+      </c>
+      <c r="B268" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="C268" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="1">
+        <v>365</v>
+      </c>
+      <c r="B269" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C269" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="1">
+        <v>403</v>
+      </c>
+      <c r="B270" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="C270" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="1">
+        <v>370</v>
+      </c>
+      <c r="B271" t="s" s="1">
+        <v>500</v>
+      </c>
+      <c r="C271" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="1">
+        <v>964</v>
+      </c>
+      <c r="B272" t="s" s="1">
+        <v>101</v>
+      </c>
+      <c r="C272" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s" s="1">
+        <v>965</v>
+      </c>
+      <c r="B273" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="C273" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s" s="1">
+        <v>966</v>
+      </c>
+      <c r="B274" t="s" s="1">
+        <v>80</v>
+      </c>
+      <c r="C274" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s" s="1">
+        <v>638</v>
+      </c>
+      <c r="B275" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="C275" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="1">
+        <v>399</v>
+      </c>
+      <c r="B276" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C276" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s" s="1">
+        <v>562</v>
+      </c>
+      <c r="B277" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="C277" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s" s="1">
+        <v>449</v>
+      </c>
+      <c r="B278" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C278" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s" s="1">
+        <v>967</v>
+      </c>
+      <c r="B279" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="C279" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s" s="1">
+        <v>329</v>
+      </c>
+      <c r="B280" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="C280" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s" s="1">
+        <v>615</v>
+      </c>
+      <c r="B281" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C281" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="1">
+        <v>968</v>
+      </c>
+      <c r="B282" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="C282" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="1">
+        <v>361</v>
+      </c>
+      <c r="B283" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="C283" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="1">
+        <v>533</v>
+      </c>
+      <c r="B284" t="s" s="1">
+        <v>107</v>
+      </c>
+      <c r="C284" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="1">
+        <v>427</v>
+      </c>
+      <c r="B285" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C285" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="1">
+        <v>367</v>
+      </c>
+      <c r="B286" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="C286" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s" s="1">
+        <v>872</v>
+      </c>
+      <c r="B287" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C287" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s" s="1">
+        <v>969</v>
+      </c>
+      <c r="B288" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C288" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s" s="1">
+        <v>970</v>
+      </c>
+      <c r="B289" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="C289" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s" s="1">
+        <v>398</v>
+      </c>
+      <c r="B290" t="s" s="1">
+        <v>80</v>
+      </c>
+      <c r="C290" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s" s="1">
+        <v>971</v>
+      </c>
+      <c r="B291" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="C291" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s" s="1">
+        <v>432</v>
+      </c>
+      <c r="B292" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="C292" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s" s="1">
+        <v>577</v>
+      </c>
+      <c r="B293" t="s" s="1">
+        <v>141</v>
+      </c>
+      <c r="C293" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s" s="1">
+        <v>972</v>
+      </c>
+      <c r="B294" t="s" s="1">
+        <v>86</v>
+      </c>
+      <c r="C294" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s" s="1">
+        <v>331</v>
+      </c>
+      <c r="B295" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="C295" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s" s="1">
+        <v>604</v>
+      </c>
+      <c r="B296" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C296" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s" s="1">
+        <v>579</v>
+      </c>
+      <c r="B297" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="C297" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s" s="1">
+        <v>422</v>
+      </c>
+      <c r="B298" t="s" s="1">
+        <v>80</v>
+      </c>
+      <c r="C298" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s" s="1">
+        <v>429</v>
+      </c>
+      <c r="B299" t="s" s="1">
+        <v>547</v>
+      </c>
+      <c r="C299" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s" s="1">
+        <v>574</v>
+      </c>
+      <c r="B300" t="s" s="1">
+        <v>130</v>
+      </c>
+      <c r="C300" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s" s="1">
+        <v>973</v>
+      </c>
+      <c r="B301" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C301" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s" s="1">
+        <v>974</v>
+      </c>
+      <c r="B302" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C302" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s" s="1">
+        <v>590</v>
+      </c>
+      <c r="B303" t="s" s="1">
+        <v>975</v>
+      </c>
+      <c r="C303" t="s" s="1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s" s="1">
+        <v>362</v>
+      </c>
+      <c r="B304" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="C304" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s" s="1">
+        <v>582</v>
+      </c>
+      <c r="B305" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C305" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s" s="1">
+        <v>445</v>
+      </c>
+      <c r="B306" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="C306" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s" s="1">
+        <v>532</v>
+      </c>
+      <c r="B307" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C307" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s" s="1">
+        <v>358</v>
+      </c>
+      <c r="B308" t="s" s="1">
+        <v>86</v>
+      </c>
+      <c r="C308" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s" s="1">
+        <v>578</v>
+      </c>
+      <c r="B309" t="s" s="1">
+        <v>217</v>
+      </c>
+      <c r="C309" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s" s="1">
+        <v>439</v>
+      </c>
+      <c r="B310" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="C310" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s" s="1">
+        <v>976</v>
+      </c>
+      <c r="B311" t="s" s="1">
+        <v>689</v>
+      </c>
+      <c r="C311" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s" s="1">
+        <v>404</v>
+      </c>
+      <c r="B312" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C312" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s" s="1">
+        <v>421</v>
+      </c>
+      <c r="B313" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="C313" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s" s="1">
+        <v>316</v>
+      </c>
+      <c r="B314" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C314" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s" s="1">
+        <v>977</v>
+      </c>
+      <c r="B315" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="C315" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s" s="1">
+        <v>978</v>
+      </c>
+      <c r="B316" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="C316" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s" s="1">
+        <v>460</v>
+      </c>
+      <c r="B317" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C317" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s" s="1">
+        <v>527</v>
+      </c>
+      <c r="B318" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C318" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s" s="1">
+        <v>979</v>
+      </c>
+      <c r="B319" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="C319" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s" s="1">
+        <v>409</v>
+      </c>
+      <c r="B320" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="C320" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s" s="1">
+        <v>564</v>
+      </c>
+      <c r="B321" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="C321" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="s" s="1">
+        <v>468</v>
+      </c>
+      <c r="B322" t="s" s="1">
+        <v>355</v>
+      </c>
+      <c r="C322" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s" s="1">
+        <v>485</v>
+      </c>
+      <c r="B323" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="C323" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="s" s="1">
+        <v>393</v>
+      </c>
+      <c r="B324" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C324" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="s" s="1">
+        <v>980</v>
+      </c>
+      <c r="B325" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C325" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="s" s="1">
+        <v>526</v>
+      </c>
+      <c r="B326" t="s" s="1">
+        <v>648</v>
+      </c>
+      <c r="C326" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s" s="1">
+        <v>981</v>
+      </c>
+      <c r="B327" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="C327" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s" s="1">
+        <v>587</v>
+      </c>
+      <c r="B328" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C328" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="s" s="1">
+        <v>982</v>
+      </c>
+      <c r="B329" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C329" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="s" s="1">
+        <v>517</v>
+      </c>
+      <c r="B330" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="C330" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="s" s="1">
+        <v>502</v>
+      </c>
+      <c r="B331" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="C331" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="s" s="1">
+        <v>571</v>
+      </c>
+      <c r="B332" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="C332" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s" s="1">
+        <v>377</v>
+      </c>
+      <c r="B333" t="s" s="1">
+        <v>215</v>
+      </c>
+      <c r="C333" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="s" s="1">
+        <v>983</v>
+      </c>
+      <c r="B334" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="C334" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="s" s="1">
+        <v>984</v>
+      </c>
+      <c r="B335" t="s" s="1">
+        <v>391</v>
+      </c>
+      <c r="C335" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s" s="1">
+        <v>985</v>
+      </c>
+      <c r="B336" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C336" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="s" s="1">
+        <v>408</v>
+      </c>
+      <c r="B337" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C337" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="s" s="1">
+        <v>528</v>
+      </c>
+      <c r="B338" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C338" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="s" s="1">
+        <v>318</v>
+      </c>
+      <c r="B339" t="s" s="1">
+        <v>75</v>
+      </c>
+      <c r="C339" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="s" s="1">
+        <v>339</v>
+      </c>
+      <c r="B340" t="s" s="1">
+        <v>116</v>
+      </c>
+      <c r="C340" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="s" s="1">
+        <v>609</v>
+      </c>
+      <c r="B341" t="s" s="1">
+        <v>69</v>
+      </c>
+      <c r="C341" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="s" s="1">
+        <v>348</v>
+      </c>
+      <c r="B342" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="C342" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="s" s="1">
+        <v>464</v>
+      </c>
+      <c r="B343" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="C343" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="s" s="1">
+        <v>438</v>
+      </c>
+      <c r="B344" t="s" s="1">
+        <v>521</v>
+      </c>
+      <c r="C344" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="s" s="1">
+        <v>553</v>
+      </c>
+      <c r="B345" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C345" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="s" s="1">
+        <v>986</v>
+      </c>
+      <c r="B346" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="C346" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="s" s="1">
+        <v>456</v>
+      </c>
+      <c r="B347" t="s" s="1">
+        <v>987</v>
+      </c>
+      <c r="C347" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="s" s="1">
+        <v>412</v>
+      </c>
+      <c r="B348" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="C348" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="s" s="1">
+        <v>514</v>
+      </c>
+      <c r="B349" t="s" s="1">
+        <v>542</v>
+      </c>
+      <c r="C349" t="s" s="1">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="s" s="1">
+        <v>988</v>
+      </c>
+      <c r="B350" t="s" s="1">
+        <v>215</v>
+      </c>
+      <c r="C350" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="s" s="1">
+        <v>989</v>
+      </c>
+      <c r="B351" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="C351" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="s" s="1">
+        <v>324</v>
+      </c>
+      <c r="B352" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C352" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="s" s="1">
+        <v>593</v>
+      </c>
+      <c r="B353" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C353" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="s" s="1">
+        <v>570</v>
+      </c>
+      <c r="B354" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="C354" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="s" s="1">
+        <v>435</v>
+      </c>
+      <c r="B355" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="C355" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="s" s="1">
+        <v>600</v>
+      </c>
+      <c r="B356" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="C356" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="s" s="1">
+        <v>990</v>
+      </c>
+      <c r="B357" t="s" s="1">
+        <v>82</v>
+      </c>
+      <c r="C357" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="s" s="1">
+        <v>511</v>
+      </c>
+      <c r="B358" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="C358" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="s" s="1">
+        <v>423</v>
+      </c>
+      <c r="B359" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="C359" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="s" s="1">
+        <v>385</v>
+      </c>
+      <c r="B360" t="s" s="1">
+        <v>355</v>
+      </c>
+      <c r="C360" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="s" s="1">
+        <v>631</v>
+      </c>
+      <c r="B361" t="s" s="1">
+        <v>542</v>
+      </c>
+      <c r="C361" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="s" s="1">
+        <v>991</v>
+      </c>
+      <c r="B362" t="s" s="1">
+        <v>141</v>
+      </c>
+      <c r="C362" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="s" s="1">
+        <v>402</v>
+      </c>
+      <c r="B363" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C363" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="s" s="1">
+        <v>368</v>
+      </c>
+      <c r="B364" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C364" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="s" s="1">
+        <v>465</v>
+      </c>
+      <c r="B365" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C365" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="s" s="1">
+        <v>357</v>
+      </c>
+      <c r="B366" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="C366" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="s" s="1">
+        <v>506</v>
+      </c>
+      <c r="B367" t="s" s="1">
+        <v>737</v>
+      </c>
+      <c r="C367" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="s" s="1">
+        <v>496</v>
+      </c>
+      <c r="B368" t="s" s="1">
+        <v>497</v>
+      </c>
+      <c r="C368" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="s" s="1">
+        <v>594</v>
+      </c>
+      <c r="B369" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="C369" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="s" s="1">
+        <v>992</v>
+      </c>
+      <c r="B370" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="C370" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="s" s="1">
+        <v>347</v>
+      </c>
+      <c r="B371" t="s" s="1">
+        <v>547</v>
+      </c>
+      <c r="C371" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="s" s="1">
+        <v>993</v>
+      </c>
+      <c r="B372" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C372" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="s" s="1">
+        <v>729</v>
+      </c>
+      <c r="B373" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="C373" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="s" s="1">
+        <v>677</v>
+      </c>
+      <c r="B374" t="s" s="1">
+        <v>107</v>
+      </c>
+      <c r="C374" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="s" s="1">
+        <v>659</v>
+      </c>
+      <c r="B375" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="C375" t="s" s="1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="s" s="1">
+        <v>994</v>
+      </c>
+      <c r="B376" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C376" t="s" s="1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="s" s="1">
+        <v>664</v>
+      </c>
+      <c r="B377" t="s" s="1">
+        <v>144</v>
+      </c>
+      <c r="C377" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="s" s="1">
+        <v>995</v>
+      </c>
+      <c r="B378" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C378" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="s" s="1">
+        <v>643</v>
+      </c>
+      <c r="B379" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="C379" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="s" s="1">
+        <v>764</v>
+      </c>
+      <c r="B380" t="s" s="1">
+        <v>155</v>
+      </c>
+      <c r="C380" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="s" s="1">
+        <v>698</v>
+      </c>
+      <c r="B381" t="s" s="1">
+        <v>207</v>
+      </c>
+      <c r="C381" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="s" s="1">
+        <v>665</v>
+      </c>
+      <c r="B382" t="s" s="1">
+        <v>996</v>
+      </c>
+      <c r="C382" t="s" s="1">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="s" s="1">
+        <v>715</v>
+      </c>
+      <c r="B383" t="s" s="1">
+        <v>86</v>
+      </c>
+      <c r="C383" t="s" s="1">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="s" s="1">
+        <v>997</v>
+      </c>
+      <c r="B384" t="s" s="1">
+        <v>67</v>
+      </c>
+      <c r="C384" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="s" s="1">
+        <v>693</v>
+      </c>
+      <c r="B385" t="s" s="1">
+        <v>49</v>
+      </c>
+      <c r="C385" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="s" s="1">
+        <v>676</v>
+      </c>
+      <c r="B386" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="C386" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="s" s="1">
+        <v>709</v>
+      </c>
+      <c r="B387" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C387" t="s" s="1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="s" s="1">
+        <v>726</v>
+      </c>
+      <c r="B388" t="s" s="1">
+        <v>535</v>
+      </c>
+      <c r="C388" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="s" s="1">
+        <v>714</v>
+      </c>
+      <c r="B389" t="s" s="1">
+        <v>118</v>
+      </c>
+      <c r="C389" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="s" s="1">
+        <v>731</v>
+      </c>
+      <c r="B390" t="s" s="1">
+        <v>144</v>
+      </c>
+      <c r="C390" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="s" s="1">
+        <v>710</v>
+      </c>
+      <c r="B391" t="s" s="1">
+        <v>560</v>
+      </c>
+      <c r="C391" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="s" s="1">
+        <v>663</v>
+      </c>
+      <c r="B392" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="C392" t="s" s="1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="s" s="1">
+        <v>685</v>
+      </c>
+      <c r="B393" t="s" s="1">
+        <v>431</v>
+      </c>
+      <c r="C393" t="s" s="1">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="s" s="1">
+        <v>695</v>
+      </c>
+      <c r="B394" t="s" s="1">
+        <v>176</v>
+      </c>
+      <c r="C394" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s" s="1">
+        <v>672</v>
+      </c>
+      <c r="B395" t="s" s="1">
+        <v>107</v>
+      </c>
+      <c r="C395" t="s" s="1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="s" s="1">
+        <v>694</v>
+      </c>
+      <c r="B396" t="s" s="1">
+        <v>101</v>
+      </c>
+      <c r="C396" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="s" s="1">
+        <v>654</v>
+      </c>
+      <c r="B397" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C397" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="s" s="1">
+        <v>645</v>
+      </c>
+      <c r="B398" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C398" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="s" s="1">
+        <v>747</v>
+      </c>
+      <c r="B399" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="C399" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="s" s="1">
+        <v>675</v>
+      </c>
+      <c r="B400" t="s" s="1">
+        <v>215</v>
+      </c>
+      <c r="C400" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="s" s="1">
+        <v>667</v>
+      </c>
+      <c r="B401" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="C401" t="s" s="1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="s" s="1">
+        <v>697</v>
+      </c>
+      <c r="B402" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="C402" t="s" s="1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="s" s="1">
+        <v>765</v>
+      </c>
+      <c r="B403" t="s" s="1">
+        <v>101</v>
+      </c>
+      <c r="C403" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="s" s="1">
+        <v>713</v>
+      </c>
+      <c r="B404" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="C404" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="s" s="1">
+        <v>998</v>
+      </c>
+      <c r="B405" t="s" s="1">
+        <v>141</v>
+      </c>
+      <c r="C405" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="s" s="1">
+        <v>754</v>
+      </c>
+      <c r="B406" t="s" s="1">
+        <v>82</v>
+      </c>
+      <c r="C406" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="s" s="1">
+        <v>641</v>
+      </c>
+      <c r="B407" t="s" s="1">
+        <v>892</v>
+      </c>
+      <c r="C407" t="s" s="1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="s" s="1">
+        <v>732</v>
+      </c>
+      <c r="B408" t="s" s="1">
+        <v>58</v>
+      </c>
+      <c r="C408" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="s" s="1">
+        <v>679</v>
+      </c>
+      <c r="B409" t="s" s="1">
+        <v>16</v>
+      </c>
+      <c r="C409" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="s" s="1">
+        <v>662</v>
+      </c>
+      <c r="B410" t="s" s="1">
+        <v>652</v>
+      </c>
+      <c r="C410" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="s" s="1">
+        <v>738</v>
+      </c>
+      <c r="B411" t="s" s="1">
+        <v>975</v>
+      </c>
+      <c r="C411" t="s" s="1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="s" s="1">
+        <v>712</v>
+      </c>
+      <c r="B412" t="s" s="1">
+        <v>82</v>
+      </c>
+      <c r="C412" t="s" s="1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="s" s="1">
+        <v>678</v>
+      </c>
+      <c r="B413" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="C413" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="s" s="1">
+        <v>661</v>
+      </c>
+      <c r="B414" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C414" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="s" s="1">
+        <v>682</v>
+      </c>
+      <c r="B415" t="s" s="1">
+        <v>576</v>
+      </c>
+      <c r="C415" t="s" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="s" s="1">
+        <v>690</v>
+      </c>
+      <c r="B416" t="s" s="1">
+        <v>772</v>
+      </c>
+      <c r="C416" t="s" s="1">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="s" s="1">
+        <v>745</v>
+      </c>
+      <c r="B417" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C417" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="s" s="1">
+        <v>703</v>
+      </c>
+      <c r="B418" t="s" s="1">
+        <v>160</v>
+      </c>
+      <c r="C418" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="s" s="1">
+        <v>722</v>
+      </c>
+      <c r="B419" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="C419" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="s" s="1">
+        <v>681</v>
+      </c>
+      <c r="B420" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="C420" t="s" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="s" s="1">
+        <v>734</v>
+      </c>
+      <c r="B421" t="s" s="1">
+        <v>999</v>
+      </c>
+      <c r="C421" t="s" s="1">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
